--- a/DataTables/Datas/Map/#MapTileContentWeight.xlsx
+++ b/DataTables/Datas/Map/#MapTileContentWeight.xlsx
@@ -12,7 +12,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'MapTileContentWeight'!$A$1:$H$9</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
 </file>
 
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C5" s="3" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="D5" s="3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>2</v>
@@ -658,10 +658,10 @@
         <v>45</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>5</v>
@@ -687,10 +687,10 @@
         <v>45</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>5</v>
@@ -716,10 +716,10 @@
         <v>30</v>
       </c>
       <c r="D8" s="3" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>15</v>
@@ -745,10 +745,10 @@
         <v>20</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>20</v>
